--- a/output/latest/SSGADD_DATA_LATEST.xlsx
+++ b/output/latest/SSGADD_DATA_LATEST.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C481"/>
+  <dimension ref="A1:C570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,8 +451,10 @@
       <c r="B3" t="n">
         <v>3.22</v>
       </c>
-      <c r="C3" t="n">
-        <v>4.06</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -464,8 +466,10 @@
       <c r="B4" t="n">
         <v>3.21</v>
       </c>
-      <c r="C4" t="n">
-        <v>4.05</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -477,8 +481,10 @@
       <c r="B5" t="n">
         <v>3.22</v>
       </c>
-      <c r="C5" t="n">
-        <v>4.06</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -490,8 +496,10 @@
       <c r="B6" t="n">
         <v>3.22</v>
       </c>
-      <c r="C6" t="n">
-        <v>4.05</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -503,8 +511,10 @@
       <c r="B7" t="n">
         <v>3.25</v>
       </c>
-      <c r="C7" t="n">
-        <v>4.04</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -516,8 +526,10 @@
       <c r="B8" t="n">
         <v>3.26</v>
       </c>
-      <c r="C8" t="n">
-        <v>4.04</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -529,8 +541,10 @@
       <c r="B9" t="n">
         <v>3.29</v>
       </c>
-      <c r="C9" t="n">
-        <v>4.08</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -542,8 +556,10 @@
       <c r="B10" t="n">
         <v>3.24</v>
       </c>
-      <c r="C10" t="n">
-        <v>4.05</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -555,8 +571,10 @@
       <c r="B11" t="n">
         <v>3.22</v>
       </c>
-      <c r="C11" t="n">
-        <v>4.04</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -568,8 +586,10 @@
       <c r="B12" t="n">
         <v>3.16</v>
       </c>
-      <c r="C12" t="n">
-        <v>4.03</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -581,8 +601,10 @@
       <c r="B13" t="n">
         <v>3.21</v>
       </c>
-      <c r="C13" t="n">
-        <v>4.02</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -594,8 +616,10 @@
       <c r="B14" t="n">
         <v>3.23</v>
       </c>
-      <c r="C14" t="n">
-        <v>4.02</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -607,8 +631,10 @@
       <c r="B15" t="n">
         <v>3.24</v>
       </c>
-      <c r="C15" t="n">
-        <v>4.04</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -620,8 +646,10 @@
       <c r="B16" t="n">
         <v>3.24</v>
       </c>
-      <c r="C16" t="n">
-        <v>4.05</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -633,8 +661,10 @@
       <c r="B17" t="n">
         <v>3.26</v>
       </c>
-      <c r="C17" t="n">
-        <v>4.06</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -646,8 +676,10 @@
       <c r="B18" t="n">
         <v>3.26</v>
       </c>
-      <c r="C18" t="n">
-        <v>4.06</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -659,8 +691,10 @@
       <c r="B19" t="n">
         <v>3.27</v>
       </c>
-      <c r="C19" t="n">
-        <v>4.04</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -672,8 +706,10 @@
       <c r="B20" t="n">
         <v>3.34</v>
       </c>
-      <c r="C20" t="n">
-        <v>4.04</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -685,8 +721,10 @@
       <c r="B21" t="n">
         <v>3.28</v>
       </c>
-      <c r="C21" t="n">
-        <v>4.04</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -698,8 +736,10 @@
       <c r="B22" t="n">
         <v>3.26</v>
       </c>
-      <c r="C22" t="n">
-        <v>4.04</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -711,8 +751,10 @@
       <c r="B23" t="n">
         <v>3.27</v>
       </c>
-      <c r="C23" t="n">
-        <v>4.04</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -724,8 +766,10 @@
       <c r="B24" t="n">
         <v>3.27</v>
       </c>
-      <c r="C24" t="n">
-        <v>4.04</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -737,8 +781,10 @@
       <c r="B25" t="n">
         <v>3.26</v>
       </c>
-      <c r="C25" t="n">
-        <v>4.04</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -750,8 +796,10 @@
       <c r="B26" t="n">
         <v>3.29</v>
       </c>
-      <c r="C26" t="n">
-        <v>4.03</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -763,8 +811,10 @@
       <c r="B27" t="n">
         <v>3.31</v>
       </c>
-      <c r="C27" t="n">
-        <v>4.03</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -776,8 +826,10 @@
       <c r="B28" t="n">
         <v>3.31</v>
       </c>
-      <c r="C28" t="n">
-        <v>4.03</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -789,8 +841,10 @@
       <c r="B29" t="n">
         <v>3.34</v>
       </c>
-      <c r="C29" t="n">
-        <v>4.02</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -802,8 +856,10 @@
       <c r="B30" t="n">
         <v>3.37</v>
       </c>
-      <c r="C30" t="n">
-        <v>4.02</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -815,8 +871,10 @@
       <c r="B31" t="n">
         <v>3.37</v>
       </c>
-      <c r="C31" t="n">
-        <v>4.03</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -828,8 +886,10 @@
       <c r="B32" t="n">
         <v>3.38</v>
       </c>
-      <c r="C32" t="n">
-        <v>4.02</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -841,8 +901,10 @@
       <c r="B33" t="n">
         <v>3.4</v>
       </c>
-      <c r="C33" t="n">
-        <v>4.02</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -854,8 +916,10 @@
       <c r="B34" t="n">
         <v>3.34</v>
       </c>
-      <c r="C34" t="n">
-        <v>4.01</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -867,8 +931,10 @@
       <c r="B35" t="n">
         <v>3.3</v>
       </c>
-      <c r="C35" t="n">
-        <v>4.01</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -880,8 +946,10 @@
       <c r="B36" t="n">
         <v>3.31</v>
       </c>
-      <c r="C36" t="n">
-        <v>4.01</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -893,8 +961,10 @@
       <c r="B37" t="n">
         <v>3.33</v>
       </c>
-      <c r="C37" t="n">
-        <v>4</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -906,8 +976,10 @@
       <c r="B38" t="n">
         <v>3.31</v>
       </c>
-      <c r="C38" t="n">
-        <v>3.98</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -919,8 +991,10 @@
       <c r="B39" t="n">
         <v>3.29</v>
       </c>
-      <c r="C39" t="n">
-        <v>4.03</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -932,8 +1006,10 @@
       <c r="B40" t="n">
         <v>3.34</v>
       </c>
-      <c r="C40" t="n">
-        <v>4.09</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -945,8 +1021,10 @@
       <c r="B41" t="n">
         <v>3.33</v>
       </c>
-      <c r="C41" t="n">
-        <v>4.1</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -958,8 +1036,10 @@
       <c r="B42" t="n">
         <v>3.29</v>
       </c>
-      <c r="C42" t="n">
-        <v>4.07</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -971,8 +1051,10 @@
       <c r="B43" t="n">
         <v>3.16</v>
       </c>
-      <c r="C43" t="n">
-        <v>4.06</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -984,8 +1066,10 @@
       <c r="B44" t="n">
         <v>3.29</v>
       </c>
-      <c r="C44" t="n">
-        <v>4.07</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -997,8 +1081,10 @@
       <c r="B45" t="n">
         <v>3.22</v>
       </c>
-      <c r="C45" t="n">
-        <v>4.08</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1010,8 +1096,10 @@
       <c r="B46" t="n">
         <v>3.26</v>
       </c>
-      <c r="C46" t="n">
-        <v>4.08</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1023,8 +1111,10 @@
       <c r="B47" t="n">
         <v>3.26</v>
       </c>
-      <c r="C47" t="n">
-        <v>4.07</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1036,8 +1126,10 @@
       <c r="B48" t="n">
         <v>3.27</v>
       </c>
-      <c r="C48" t="n">
-        <v>4.06</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1049,8 +1141,10 @@
       <c r="B49" t="n">
         <v>3.27</v>
       </c>
-      <c r="C49" t="n">
-        <v>4.11</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1062,8 +1156,10 @@
       <c r="B50" t="n">
         <v>3.26</v>
       </c>
-      <c r="C50" t="n">
-        <v>4.09</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1075,8 +1171,10 @@
       <c r="B51" t="n">
         <v>3.24</v>
       </c>
-      <c r="C51" t="n">
-        <v>4.07</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1088,8 +1186,10 @@
       <c r="B52" t="n">
         <v>3.22</v>
       </c>
-      <c r="C52" t="n">
-        <v>4.07</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -1101,8 +1201,10 @@
       <c r="B53" t="n">
         <v>3.25</v>
       </c>
-      <c r="C53" t="n">
-        <v>4.06</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1114,8 +1216,10 @@
       <c r="B54" t="n">
         <v>3.25</v>
       </c>
-      <c r="C54" t="n">
-        <v>4.06</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1127,8 +1231,10 @@
       <c r="B55" t="n">
         <v>3.22</v>
       </c>
-      <c r="C55" t="n">
-        <v>4.07</v>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1140,8 +1246,10 @@
       <c r="B56" t="n">
         <v>3.24</v>
       </c>
-      <c r="C56" t="n">
-        <v>4.06</v>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1153,8 +1261,10 @@
       <c r="B57" t="n">
         <v>3.32</v>
       </c>
-      <c r="C57" t="n">
-        <v>4.07</v>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -1166,8 +1276,10 @@
       <c r="B58" t="n">
         <v>3.31</v>
       </c>
-      <c r="C58" t="n">
-        <v>4.06</v>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1179,8 +1291,10 @@
       <c r="B59" t="n">
         <v>3.31</v>
       </c>
-      <c r="C59" t="n">
-        <v>4.06</v>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -1192,8 +1306,10 @@
       <c r="B60" t="n">
         <v>3.3</v>
       </c>
-      <c r="C60" t="n">
-        <v>4.05</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -1205,8 +1321,10 @@
       <c r="B61" t="n">
         <v>3.33</v>
       </c>
-      <c r="C61" t="n">
-        <v>4.04</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -1218,8 +1336,10 @@
       <c r="B62" t="n">
         <v>3.25</v>
       </c>
-      <c r="C62" t="n">
-        <v>4.03</v>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -1231,8 +1351,10 @@
       <c r="B63" t="n">
         <v>3.31</v>
       </c>
-      <c r="C63" t="n">
-        <v>4.06</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1244,8 +1366,10 @@
       <c r="B64" t="n">
         <v>3.26</v>
       </c>
-      <c r="C64" t="n">
-        <v>4.05</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -1257,8 +1381,10 @@
       <c r="B65" t="n">
         <v>3.26</v>
       </c>
-      <c r="C65" t="n">
-        <v>4.1</v>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -1270,8 +1396,10 @@
       <c r="B66" t="n">
         <v>3.19</v>
       </c>
-      <c r="C66" t="n">
-        <v>4.04</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -1283,8 +1411,10 @@
       <c r="B67" t="n">
         <v>3.21</v>
       </c>
-      <c r="C67" t="n">
-        <v>4.09</v>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -1296,8 +1426,10 @@
       <c r="B68" t="n">
         <v>3.26</v>
       </c>
-      <c r="C68" t="n">
-        <v>4.07</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -1309,8 +1441,10 @@
       <c r="B69" t="n">
         <v>3.26</v>
       </c>
-      <c r="C69" t="n">
-        <v>4.04</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -1322,8 +1456,10 @@
       <c r="B70" t="n">
         <v>3.25</v>
       </c>
-      <c r="C70" t="n">
-        <v>4.03</v>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -1335,8 +1471,10 @@
       <c r="B71" t="n">
         <v>3.07</v>
       </c>
-      <c r="C71" t="n">
-        <v>4.03</v>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -1348,8 +1486,10 @@
       <c r="B72" t="n">
         <v>3.26</v>
       </c>
-      <c r="C72" t="n">
-        <v>4.07</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -1361,8 +1501,10 @@
       <c r="B73" t="n">
         <v>3.22</v>
       </c>
-      <c r="C73" t="n">
-        <v>4.03</v>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -1374,8 +1516,10 @@
       <c r="B74" t="n">
         <v>3.22</v>
       </c>
-      <c r="C74" t="n">
-        <v>4.02</v>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -1387,8 +1531,10 @@
       <c r="B75" t="n">
         <v>3.21</v>
       </c>
-      <c r="C75" t="n">
-        <v>4.04</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -1400,8 +1546,10 @@
       <c r="B76" t="n">
         <v>3.21</v>
       </c>
-      <c r="C76" t="n">
-        <v>4.04</v>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -1413,8 +1561,10 @@
       <c r="B77" t="n">
         <v>3.22</v>
       </c>
-      <c r="C77" t="n">
-        <v>4.03</v>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -1426,8 +1576,10 @@
       <c r="B78" t="n">
         <v>3.21</v>
       </c>
-      <c r="C78" t="n">
-        <v>4.03</v>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -1439,8 +1591,10 @@
       <c r="B79" t="n">
         <v>3.2</v>
       </c>
-      <c r="C79" t="n">
-        <v>4.02</v>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -1452,8 +1606,10 @@
       <c r="B80" t="n">
         <v>3.2</v>
       </c>
-      <c r="C80" t="n">
-        <v>4.02</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -1465,8 +1621,10 @@
       <c r="B81" t="n">
         <v>3.23</v>
       </c>
-      <c r="C81" t="n">
-        <v>4.02</v>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -1478,8 +1636,10 @@
       <c r="B82" t="n">
         <v>3.27</v>
       </c>
-      <c r="C82" t="n">
-        <v>4.02</v>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -1491,8 +1651,10 @@
       <c r="B83" t="n">
         <v>3.27</v>
       </c>
-      <c r="C83" t="n">
-        <v>4.08</v>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -1504,8 +1666,10 @@
       <c r="B84" t="n">
         <v>3.29</v>
       </c>
-      <c r="C84" t="n">
-        <v>4.12</v>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -1517,8 +1681,10 @@
       <c r="B85" t="n">
         <v>3.22</v>
       </c>
-      <c r="C85" t="n">
-        <v>4.02</v>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -1530,8 +1696,10 @@
       <c r="B86" t="n">
         <v>3.21</v>
       </c>
-      <c r="C86" t="n">
-        <v>4.04</v>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -1543,8 +1711,10 @@
       <c r="B87" t="n">
         <v>3.21</v>
       </c>
-      <c r="C87" t="n">
-        <v>4.04</v>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -1556,8 +1726,10 @@
       <c r="B88" t="n">
         <v>3.17</v>
       </c>
-      <c r="C88" t="n">
-        <v>4.04</v>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -1569,8 +1741,10 @@
       <c r="B89" t="n">
         <v>3.16</v>
       </c>
-      <c r="C89" t="n">
-        <v>4.03</v>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -1582,8 +1756,10 @@
       <c r="B90" t="n">
         <v>3.17</v>
       </c>
-      <c r="C90" t="n">
-        <v>4.02</v>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -1595,8 +1771,10 @@
       <c r="B91" t="n">
         <v>3.16</v>
       </c>
-      <c r="C91" t="n">
-        <v>4.01</v>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -1608,8 +1786,10 @@
       <c r="B92" t="n">
         <v>3.12</v>
       </c>
-      <c r="C92" t="n">
-        <v>4.01</v>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -1621,8 +1801,10 @@
       <c r="B93" t="n">
         <v>3.11</v>
       </c>
-      <c r="C93" t="n">
-        <v>4.01</v>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -1634,8 +1816,10 @@
       <c r="B94" t="n">
         <v>3.12</v>
       </c>
-      <c r="C94" t="n">
-        <v>4.01</v>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -1647,8 +1831,10 @@
       <c r="B95" t="n">
         <v>3.09</v>
       </c>
-      <c r="C95" t="n">
-        <v>4.01</v>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -1660,8 +1846,10 @@
       <c r="B96" t="n">
         <v>3.1</v>
       </c>
-      <c r="C96" t="n">
-        <v>4.01</v>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -1673,8 +1861,10 @@
       <c r="B97" t="n">
         <v>3.12</v>
       </c>
-      <c r="C97" t="n">
-        <v>4.01</v>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -1686,8 +1876,10 @@
       <c r="B98" t="n">
         <v>3.13</v>
       </c>
-      <c r="C98" t="n">
-        <v>4.01</v>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -1699,8 +1891,10 @@
       <c r="B99" t="n">
         <v>3.12</v>
       </c>
-      <c r="C99" t="n">
-        <v>4.01</v>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -1712,8 +1906,10 @@
       <c r="B100" t="n">
         <v>3.13</v>
       </c>
-      <c r="C100" t="n">
-        <v>4</v>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -1725,8 +1921,10 @@
       <c r="B101" t="n">
         <v>3.13</v>
       </c>
-      <c r="C101" t="n">
-        <v>4.08</v>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -1738,8 +1936,10 @@
       <c r="B102" t="n">
         <v>3.14</v>
       </c>
-      <c r="C102" t="n">
-        <v>4.03</v>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -1751,8 +1951,10 @@
       <c r="B103" t="n">
         <v>3.12</v>
       </c>
-      <c r="C103" t="n">
-        <v>4.01</v>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -1764,8 +1966,10 @@
       <c r="B104" t="n">
         <v>3.12</v>
       </c>
-      <c r="C104" t="n">
-        <v>4.02</v>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -1777,8 +1981,10 @@
       <c r="B105" t="n">
         <v>3.12</v>
       </c>
-      <c r="C105" t="n">
-        <v>4</v>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -1790,8 +1996,10 @@
       <c r="B106" t="n">
         <v>3.15</v>
       </c>
-      <c r="C106" t="n">
-        <v>4.06</v>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -1803,8 +2011,10 @@
       <c r="B107" t="n">
         <v>3.16</v>
       </c>
-      <c r="C107" t="n">
-        <v>4.06</v>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -1816,8 +2026,10 @@
       <c r="B108" t="n">
         <v>3.17</v>
       </c>
-      <c r="C108" t="n">
-        <v>4.08</v>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -1829,8 +2041,10 @@
       <c r="B109" t="n">
         <v>3.21</v>
       </c>
-      <c r="C109" t="n">
-        <v>4.04</v>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -1842,8 +2056,10 @@
       <c r="B110" t="n">
         <v>3.18</v>
       </c>
-      <c r="C110" t="n">
-        <v>4.06</v>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -1855,8 +2071,10 @@
       <c r="B111" t="n">
         <v>3.17</v>
       </c>
-      <c r="C111" t="n">
-        <v>4.05</v>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -1868,8 +2086,10 @@
       <c r="B112" t="n">
         <v>3.17</v>
       </c>
-      <c r="C112" t="n">
-        <v>4.05</v>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -1881,8 +2101,10 @@
       <c r="B113" t="n">
         <v>3.16</v>
       </c>
-      <c r="C113" t="n">
-        <v>4.05</v>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -1894,8 +2116,10 @@
       <c r="B114" t="n">
         <v>3.15</v>
       </c>
-      <c r="C114" t="n">
-        <v>4.06</v>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -1907,8 +2131,10 @@
       <c r="B115" t="n">
         <v>3.14</v>
       </c>
-      <c r="C115" t="n">
-        <v>4.04</v>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -1920,8 +2146,10 @@
       <c r="B116" t="n">
         <v>3.13</v>
       </c>
-      <c r="C116" t="n">
-        <v>4.04</v>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -1933,8 +2161,10 @@
       <c r="B117" t="n">
         <v>3.14</v>
       </c>
-      <c r="C117" t="n">
-        <v>4.02</v>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -1946,8 +2176,10 @@
       <c r="B118" t="n">
         <v>3.02</v>
       </c>
-      <c r="C118" t="n">
-        <v>4.06</v>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -1959,8 +2191,10 @@
       <c r="B119" t="n">
         <v>3.08</v>
       </c>
-      <c r="C119" t="n">
-        <v>4.07</v>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -1972,8 +2206,10 @@
       <c r="B120" t="n">
         <v>3.03</v>
       </c>
-      <c r="C120" t="n">
-        <v>4.06</v>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -1985,8 +2221,10 @@
       <c r="B121" t="n">
         <v>3.01</v>
       </c>
-      <c r="C121" t="n">
-        <v>4.05</v>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -1998,8 +2236,10 @@
       <c r="B122" t="n">
         <v>3.02</v>
       </c>
-      <c r="C122" t="n">
-        <v>4.05</v>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -2011,8 +2251,10 @@
       <c r="B123" t="n">
         <v>3.02</v>
       </c>
-      <c r="C123" t="n">
-        <v>4.05</v>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -2024,8 +2266,10 @@
       <c r="B124" t="n">
         <v>3</v>
       </c>
-      <c r="C124" t="n">
-        <v>4.04</v>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -2037,8 +2281,10 @@
       <c r="B125" t="n">
         <v>3.06</v>
       </c>
-      <c r="C125" t="n">
-        <v>4.07</v>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -2050,8 +2296,10 @@
       <c r="B126" t="n">
         <v>3.06</v>
       </c>
-      <c r="C126" t="n">
-        <v>4.07</v>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -2063,8 +2311,10 @@
       <c r="B127" t="n">
         <v>3.03</v>
       </c>
-      <c r="C127" t="n">
-        <v>3.94</v>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -2076,8 +2326,10 @@
       <c r="B128" t="n">
         <v>3.04</v>
       </c>
-      <c r="C128" t="n">
-        <v>4.11</v>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -2089,8 +2341,10 @@
       <c r="B129" t="n">
         <v>3.01</v>
       </c>
-      <c r="C129" t="n">
-        <v>4.11</v>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -2102,8 +2356,10 @@
       <c r="B130" t="n">
         <v>3.03</v>
       </c>
-      <c r="C130" t="n">
-        <v>4.11</v>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -2115,8 +2371,10 @@
       <c r="B131" t="n">
         <v>3.02</v>
       </c>
-      <c r="C131" t="n">
-        <v>4.12</v>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -2128,8 +2386,10 @@
       <c r="B132" t="n">
         <v>3.02</v>
       </c>
-      <c r="C132" t="n">
-        <v>4.11</v>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -2141,8 +2401,10 @@
       <c r="B133" t="n">
         <v>3.03</v>
       </c>
-      <c r="C133" t="n">
-        <v>4.11</v>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -2154,8 +2416,10 @@
       <c r="B134" t="n">
         <v>3.03</v>
       </c>
-      <c r="C134" t="n">
-        <v>4.11</v>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -2167,8 +2431,10 @@
       <c r="B135" t="n">
         <v>3.02</v>
       </c>
-      <c r="C135" t="n">
-        <v>4.13</v>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -2180,8 +2446,10 @@
       <c r="B136" t="n">
         <v>3</v>
       </c>
-      <c r="C136" t="n">
-        <v>4.14</v>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -2193,8 +2461,10 @@
       <c r="B137" t="n">
         <v>2.99</v>
       </c>
-      <c r="C137" t="n">
-        <v>4.11</v>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -2206,8 +2476,10 @@
       <c r="B138" t="n">
         <v>3</v>
       </c>
-      <c r="C138" t="n">
-        <v>4.11</v>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -2219,8 +2491,10 @@
       <c r="B139" t="n">
         <v>2.98</v>
       </c>
-      <c r="C139" t="n">
-        <v>4.11</v>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -2232,8 +2506,10 @@
       <c r="B140" t="n">
         <v>3</v>
       </c>
-      <c r="C140" t="n">
-        <v>4.12</v>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -2245,8 +2521,10 @@
       <c r="B141" t="n">
         <v>3.04</v>
       </c>
-      <c r="C141" t="n">
-        <v>4.07</v>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -2258,8 +2536,10 @@
       <c r="B142" t="n">
         <v>3.02</v>
       </c>
-      <c r="C142" t="n">
-        <v>4.1</v>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -2271,8 +2551,10 @@
       <c r="B143" t="n">
         <v>3.04</v>
       </c>
-      <c r="C143" t="n">
-        <v>4.09</v>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -2284,8 +2566,10 @@
       <c r="B144" t="n">
         <v>3.03</v>
       </c>
-      <c r="C144" t="n">
-        <v>4.1</v>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -2297,8 +2581,10 @@
       <c r="B145" t="n">
         <v>3.01</v>
       </c>
-      <c r="C145" t="n">
-        <v>4.1</v>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -2310,8 +2596,10 @@
       <c r="B146" t="n">
         <v>3.02</v>
       </c>
-      <c r="C146" t="n">
-        <v>4.11</v>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -2323,8 +2611,10 @@
       <c r="B147" t="n">
         <v>3.02</v>
       </c>
-      <c r="C147" t="n">
-        <v>4.11</v>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -2336,8 +2626,10 @@
       <c r="B148" t="n">
         <v>3.03</v>
       </c>
-      <c r="C148" t="n">
-        <v>4.11</v>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -2349,8 +2641,10 @@
       <c r="B149" t="n">
         <v>3.05</v>
       </c>
-      <c r="C149" t="n">
-        <v>4.09</v>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -2362,8 +2656,10 @@
       <c r="B150" t="n">
         <v>3.06</v>
       </c>
-      <c r="C150" t="n">
-        <v>4.11</v>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -2375,8 +2671,10 @@
       <c r="B151" t="n">
         <v>3.09</v>
       </c>
-      <c r="C151" t="n">
-        <v>4.1</v>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -2388,8 +2686,10 @@
       <c r="B152" t="n">
         <v>3.09</v>
       </c>
-      <c r="C152" t="n">
-        <v>4.1</v>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -2401,8 +2701,10 @@
       <c r="B153" t="n">
         <v>3.1</v>
       </c>
-      <c r="C153" t="n">
-        <v>4.1</v>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -2414,8 +2716,10 @@
       <c r="B154" t="n">
         <v>3.11</v>
       </c>
-      <c r="C154" t="n">
-        <v>4.1</v>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -2427,8 +2731,10 @@
       <c r="B155" t="n">
         <v>3.11</v>
       </c>
-      <c r="C155" t="n">
-        <v>4.1</v>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -2440,8 +2746,10 @@
       <c r="B156" t="n">
         <v>3.07</v>
       </c>
-      <c r="C156" t="n">
-        <v>4.1</v>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -2453,8 +2761,10 @@
       <c r="B157" t="n">
         <v>3.06</v>
       </c>
-      <c r="C157" t="n">
-        <v>4.09</v>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -2466,8 +2776,10 @@
       <c r="B158" t="n">
         <v>3.08</v>
       </c>
-      <c r="C158" t="n">
-        <v>4.08</v>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -2479,8 +2791,10 @@
       <c r="B159" t="n">
         <v>3.08</v>
       </c>
-      <c r="C159" t="n">
-        <v>4.08</v>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -2492,8 +2806,10 @@
       <c r="B160" t="n">
         <v>3.11</v>
       </c>
-      <c r="C160" t="n">
-        <v>4.07</v>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -2505,8 +2821,10 @@
       <c r="B161" t="n">
         <v>3.13</v>
       </c>
-      <c r="C161" t="n">
-        <v>4.09</v>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -2518,8 +2836,10 @@
       <c r="B162" t="n">
         <v>3.15</v>
       </c>
-      <c r="C162" t="n">
-        <v>4.08</v>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -2531,8 +2851,10 @@
       <c r="B163" t="n">
         <v>3.19</v>
       </c>
-      <c r="C163" t="n">
-        <v>4.09</v>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -2544,8 +2866,10 @@
       <c r="B164" t="n">
         <v>3.16</v>
       </c>
-      <c r="C164" t="n">
-        <v>4.08</v>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -2557,8 +2881,10 @@
       <c r="B165" t="n">
         <v>3.15</v>
       </c>
-      <c r="C165" t="n">
-        <v>4.07</v>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -2570,8 +2896,10 @@
       <c r="B166" t="n">
         <v>3.15</v>
       </c>
-      <c r="C166" t="n">
-        <v>4.07</v>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -2583,8 +2911,10 @@
       <c r="B167" t="n">
         <v>3.15</v>
       </c>
-      <c r="C167" t="n">
-        <v>4.09</v>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -2596,8 +2926,10 @@
       <c r="B168" t="n">
         <v>3.22</v>
       </c>
-      <c r="C168" t="n">
-        <v>4.12</v>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -2609,8 +2941,10 @@
       <c r="B169" t="n">
         <v>3.21</v>
       </c>
-      <c r="C169" t="n">
-        <v>4.1</v>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -2622,8 +2956,10 @@
       <c r="B170" t="n">
         <v>3.17</v>
       </c>
-      <c r="C170" t="n">
-        <v>4.09</v>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -2635,8 +2971,10 @@
       <c r="B171" t="n">
         <v>3.17</v>
       </c>
-      <c r="C171" t="n">
-        <v>4.09</v>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -2648,8 +2986,10 @@
       <c r="B172" t="n">
         <v>3.17</v>
       </c>
-      <c r="C172" t="n">
-        <v>4.09</v>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="173">
@@ -2661,8 +3001,10 @@
       <c r="B173" t="n">
         <v>3.14</v>
       </c>
-      <c r="C173" t="n">
-        <v>4.09</v>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -2674,8 +3016,10 @@
       <c r="B174" t="n">
         <v>3.09</v>
       </c>
-      <c r="C174" t="n">
-        <v>4.09</v>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -2687,8 +3031,10 @@
       <c r="B175" t="n">
         <v>3.14</v>
       </c>
-      <c r="C175" t="n">
-        <v>4.08</v>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -2700,8 +3046,10 @@
       <c r="B176" t="n">
         <v>3.12</v>
       </c>
-      <c r="C176" t="n">
-        <v>4.09</v>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -2713,8 +3061,10 @@
       <c r="B177" t="n">
         <v>3.13</v>
       </c>
-      <c r="C177" t="n">
-        <v>4.08</v>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -2726,8 +3076,10 @@
       <c r="B178" t="n">
         <v>3.16</v>
       </c>
-      <c r="C178" t="n">
-        <v>4.08</v>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -2739,8 +3091,10 @@
       <c r="B179" t="n">
         <v>3.12</v>
       </c>
-      <c r="C179" t="n">
-        <v>4.07</v>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="180">
@@ -2752,8 +3106,10 @@
       <c r="B180" t="n">
         <v>3.14</v>
       </c>
-      <c r="C180" t="n">
-        <v>4.07</v>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -2765,8 +3121,10 @@
       <c r="B181" t="n">
         <v>3.14</v>
       </c>
-      <c r="C181" t="n">
-        <v>4.08</v>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -2778,8 +3136,10 @@
       <c r="B182" t="n">
         <v>3.07</v>
       </c>
-      <c r="C182" t="n">
-        <v>4.15</v>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
       </c>
     </row>
     <row r="183">
@@ -2791,8 +3151,10 @@
       <c r="B183" t="n">
         <v>3.12</v>
       </c>
-      <c r="C183" t="n">
-        <v>4.09</v>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="184">
@@ -2804,8 +3166,10 @@
       <c r="B184" t="n">
         <v>3.06</v>
       </c>
-      <c r="C184" t="n">
-        <v>4.11</v>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="185">
@@ -2817,8 +3181,10 @@
       <c r="B185" t="n">
         <v>3.08</v>
       </c>
-      <c r="C185" t="n">
-        <v>4.1</v>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -2830,8 +3196,10 @@
       <c r="B186" t="n">
         <v>3.07</v>
       </c>
-      <c r="C186" t="n">
-        <v>4.11</v>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="187">
@@ -2843,8 +3211,10 @@
       <c r="B187" t="n">
         <v>3.07</v>
       </c>
-      <c r="C187" t="n">
-        <v>4.11</v>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="188">
@@ -2856,8 +3226,10 @@
       <c r="B188" t="n">
         <v>3.09</v>
       </c>
-      <c r="C188" t="n">
-        <v>4.11</v>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -2869,8 +3241,10 @@
       <c r="B189" t="n">
         <v>3.07</v>
       </c>
-      <c r="C189" t="n">
-        <v>4.11</v>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="190">
@@ -2882,8 +3256,10 @@
       <c r="B190" t="n">
         <v>3.06</v>
       </c>
-      <c r="C190" t="n">
-        <v>4.09</v>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -2895,8 +3271,10 @@
       <c r="B191" t="n">
         <v>3.05</v>
       </c>
-      <c r="C191" t="n">
-        <v>4.09</v>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -2908,8 +3286,10 @@
       <c r="B192" t="n">
         <v>3.05</v>
       </c>
-      <c r="C192" t="n">
-        <v>4.09</v>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -2921,8 +3301,10 @@
       <c r="B193" t="n">
         <v>3.04</v>
       </c>
-      <c r="C193" t="n">
-        <v>4.1</v>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -2934,8 +3316,10 @@
       <c r="B194" t="n">
         <v>3.03</v>
       </c>
-      <c r="C194" t="n">
-        <v>4.08</v>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="195">
@@ -2947,8 +3331,10 @@
       <c r="B195" t="n">
         <v>3.04</v>
       </c>
-      <c r="C195" t="n">
-        <v>4.08</v>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -2960,8 +3346,10 @@
       <c r="B196" t="n">
         <v>3.05</v>
       </c>
-      <c r="C196" t="n">
-        <v>4.08</v>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -2973,8 +3361,10 @@
       <c r="B197" t="n">
         <v>3.07</v>
       </c>
-      <c r="C197" t="n">
-        <v>4.08</v>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -2986,8 +3376,10 @@
       <c r="B198" t="n">
         <v>3.1</v>
       </c>
-      <c r="C198" t="n">
-        <v>4.09</v>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="199">
@@ -2999,8 +3391,10 @@
       <c r="B199" t="n">
         <v>3.1</v>
       </c>
-      <c r="C199" t="n">
-        <v>4.08</v>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="200">
@@ -3012,8 +3406,10 @@
       <c r="B200" t="n">
         <v>3.12</v>
       </c>
-      <c r="C200" t="n">
-        <v>4.07</v>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="201">
@@ -3025,8 +3421,10 @@
       <c r="B201" t="n">
         <v>3.19</v>
       </c>
-      <c r="C201" t="n">
-        <v>4.1</v>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -3038,8 +3436,10 @@
       <c r="B202" t="n">
         <v>3.23</v>
       </c>
-      <c r="C202" t="n">
-        <v>4.09</v>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="203">
@@ -3051,8 +3451,10 @@
       <c r="B203" t="n">
         <v>3.21</v>
       </c>
-      <c r="C203" t="n">
-        <v>4.09</v>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -3064,8 +3466,10 @@
       <c r="B204" t="n">
         <v>3.2</v>
       </c>
-      <c r="C204" t="n">
-        <v>4.07</v>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -3077,8 +3481,10 @@
       <c r="B205" t="n">
         <v>3.2</v>
       </c>
-      <c r="C205" t="n">
-        <v>4.07</v>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -3090,8 +3496,10 @@
       <c r="B206" t="n">
         <v>3.2</v>
       </c>
-      <c r="C206" t="n">
-        <v>4.07</v>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -3103,8 +3511,10 @@
       <c r="B207" t="n">
         <v>3.18</v>
       </c>
-      <c r="C207" t="n">
-        <v>4.06</v>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -3116,8 +3526,10 @@
       <c r="B208" t="n">
         <v>3.2</v>
       </c>
-      <c r="C208" t="n">
-        <v>4.06</v>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -3129,8 +3541,10 @@
       <c r="B209" t="n">
         <v>3.19</v>
       </c>
-      <c r="C209" t="n">
-        <v>4.05</v>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -3142,8 +3556,10 @@
       <c r="B210" t="n">
         <v>3.27</v>
       </c>
-      <c r="C210" t="n">
-        <v>4.06</v>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -3155,8 +3571,10 @@
       <c r="B211" t="n">
         <v>3.27</v>
       </c>
-      <c r="C211" t="n">
-        <v>4.06</v>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -3168,8 +3586,10 @@
       <c r="B212" t="n">
         <v>3.18</v>
       </c>
-      <c r="C212" t="n">
-        <v>4.06</v>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -3181,8 +3601,10 @@
       <c r="B213" t="n">
         <v>3.16</v>
       </c>
-      <c r="C213" t="n">
-        <v>4.06</v>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -3194,8 +3616,10 @@
       <c r="B214" t="n">
         <v>3.14</v>
       </c>
-      <c r="C214" t="n">
-        <v>4.07</v>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="215">
@@ -3207,8 +3631,10 @@
       <c r="B215" t="n">
         <v>3.17</v>
       </c>
-      <c r="C215" t="n">
-        <v>4.06</v>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -3220,8 +3646,10 @@
       <c r="B216" t="n">
         <v>3.17</v>
       </c>
-      <c r="C216" t="n">
-        <v>4.07</v>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="217">
@@ -3233,8 +3661,10 @@
       <c r="B217" t="n">
         <v>3.17</v>
       </c>
-      <c r="C217" t="n">
-        <v>4.07</v>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -3246,8 +3676,10 @@
       <c r="B218" t="n">
         <v>3.2</v>
       </c>
-      <c r="C218" t="n">
-        <v>4.06</v>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="219">
@@ -3259,8 +3691,10 @@
       <c r="B219" t="n">
         <v>3.21</v>
       </c>
-      <c r="C219" t="n">
-        <v>4.05</v>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -3272,8 +3706,10 @@
       <c r="B220" t="n">
         <v>3.21</v>
       </c>
-      <c r="C220" t="n">
-        <v>4.05</v>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="221">
@@ -3285,8 +3721,10 @@
       <c r="B221" t="n">
         <v>3.13</v>
       </c>
-      <c r="C221" t="n">
-        <v>4.05</v>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -3298,8 +3736,10 @@
       <c r="B222" t="n">
         <v>3.12</v>
       </c>
-      <c r="C222" t="n">
-        <v>4.18</v>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -3311,8 +3751,10 @@
       <c r="B223" t="n">
         <v>3.11</v>
       </c>
-      <c r="C223" t="n">
-        <v>4.06</v>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="224">
@@ -3324,8 +3766,10 @@
       <c r="B224" t="n">
         <v>3.11</v>
       </c>
-      <c r="C224" t="n">
-        <v>4.06</v>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -3337,8 +3781,10 @@
       <c r="B225" t="n">
         <v>3.08</v>
       </c>
-      <c r="C225" t="n">
-        <v>4.04</v>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="226">
@@ -3350,8 +3796,10 @@
       <c r="B226" t="n">
         <v>3.08</v>
       </c>
-      <c r="C226" t="n">
-        <v>4.03</v>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="227">
@@ -3363,8 +3811,10 @@
       <c r="B227" t="n">
         <v>3.1</v>
       </c>
-      <c r="C227" t="n">
-        <v>4.02</v>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="228">
@@ -3376,8 +3826,10 @@
       <c r="B228" t="n">
         <v>3.1</v>
       </c>
-      <c r="C228" t="n">
-        <v>4.01</v>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="229">
@@ -3389,8 +3841,10 @@
       <c r="B229" t="n">
         <v>3.07</v>
       </c>
-      <c r="C229" t="n">
-        <v>3.99</v>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
       </c>
     </row>
     <row r="230">
@@ -3402,8 +3856,10 @@
       <c r="B230" t="n">
         <v>3.06</v>
       </c>
-      <c r="C230" t="n">
-        <v>3.99</v>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
       </c>
     </row>
     <row r="231">
@@ -3415,8 +3871,10 @@
       <c r="B231" t="n">
         <v>3.08</v>
       </c>
-      <c r="C231" t="n">
-        <v>3.99</v>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -3428,8 +3886,10 @@
       <c r="B232" t="n">
         <v>3.08</v>
       </c>
-      <c r="C232" t="n">
-        <v>4</v>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="233">
@@ -3441,8 +3901,10 @@
       <c r="B233" t="n">
         <v>3.12</v>
       </c>
-      <c r="C233" t="n">
-        <v>4.01</v>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -3454,8 +3916,10 @@
       <c r="B234" t="n">
         <v>3.13</v>
       </c>
-      <c r="C234" t="n">
-        <v>4</v>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="235">
@@ -3467,8 +3931,10 @@
       <c r="B235" t="n">
         <v>3.11</v>
       </c>
-      <c r="C235" t="n">
-        <v>3.99</v>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -3480,8 +3946,10 @@
       <c r="B236" t="n">
         <v>3.05</v>
       </c>
-      <c r="C236" t="n">
-        <v>4.01</v>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="237">
@@ -3493,8 +3961,10 @@
       <c r="B237" t="n">
         <v>3.06</v>
       </c>
-      <c r="C237" t="n">
-        <v>4.02</v>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="238">
@@ -3506,8 +3976,10 @@
       <c r="B238" t="n">
         <v>3.09</v>
       </c>
-      <c r="C238" t="n">
-        <v>4.01</v>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="239">
@@ -3519,8 +3991,10 @@
       <c r="B239" t="n">
         <v>3.09</v>
       </c>
-      <c r="C239" t="n">
-        <v>4.02</v>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="240">
@@ -3532,8 +4006,10 @@
       <c r="B240" t="n">
         <v>3.11</v>
       </c>
-      <c r="C240" t="n">
-        <v>4.01</v>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="241">
@@ -3545,8 +4021,10 @@
       <c r="B241" t="n">
         <v>3.1</v>
       </c>
-      <c r="C241" t="n">
-        <v>3.99</v>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
       </c>
     </row>
     <row r="242">
@@ -3558,8 +4036,10 @@
       <c r="B242" t="n">
         <v>3.09</v>
       </c>
-      <c r="C242" t="n">
-        <v>4.01</v>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="243">
@@ -3571,8 +4051,10 @@
       <c r="B243" t="n">
         <v>3.06</v>
       </c>
-      <c r="C243" t="n">
-        <v>4.01</v>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="244">
@@ -3584,8 +4066,10 @@
       <c r="B244" t="n">
         <v>3.06</v>
       </c>
-      <c r="C244" t="n">
-        <v>4.01</v>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -3597,8 +4081,10 @@
       <c r="B245" t="n">
         <v>3.09</v>
       </c>
-      <c r="C245" t="n">
-        <v>4.01</v>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="246">
@@ -3610,8 +4096,10 @@
       <c r="B246" t="n">
         <v>3.14</v>
       </c>
-      <c r="C246" t="n">
-        <v>4</v>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="247">
@@ -3623,8 +4111,10 @@
       <c r="B247" t="n">
         <v>3.11</v>
       </c>
-      <c r="C247" t="n">
-        <v>4.02</v>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="248">
@@ -3636,8 +4126,10 @@
       <c r="B248" t="n">
         <v>3.1</v>
       </c>
-      <c r="C248" t="n">
-        <v>4.02</v>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="249">
@@ -3649,8 +4141,10 @@
       <c r="B249" t="n">
         <v>3.1</v>
       </c>
-      <c r="C249" t="n">
-        <v>4.02</v>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="250">
@@ -3662,8 +4156,10 @@
       <c r="B250" t="n">
         <v>2.97</v>
       </c>
-      <c r="C250" t="n">
-        <v>3.85</v>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -3675,8 +4171,10 @@
       <c r="B251" t="n">
         <v>3.06</v>
       </c>
-      <c r="C251" t="n">
-        <v>4.16</v>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
       </c>
     </row>
     <row r="252">
@@ -3688,8 +4186,10 @@
       <c r="B252" t="n">
         <v>3.09</v>
       </c>
-      <c r="C252" t="n">
-        <v>4.1</v>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="253">
@@ -3701,8 +4201,10 @@
       <c r="B253" t="n">
         <v>3.08</v>
       </c>
-      <c r="C253" t="n">
-        <v>4.09</v>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="254">
@@ -3714,8 +4216,10 @@
       <c r="B254" t="n">
         <v>3.07</v>
       </c>
-      <c r="C254" t="n">
-        <v>4.11</v>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="255">
@@ -3727,8 +4231,10 @@
       <c r="B255" t="n">
         <v>3.09</v>
       </c>
-      <c r="C255" t="n">
-        <v>4.1</v>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="256">
@@ -3740,8 +4246,10 @@
       <c r="B256" t="n">
         <v>3.1</v>
       </c>
-      <c r="C256" t="n">
-        <v>4.09</v>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="257">
@@ -3753,8 +4261,10 @@
       <c r="B257" t="n">
         <v>3.13</v>
       </c>
-      <c r="C257" t="n">
-        <v>4.1</v>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="258">
@@ -3766,8 +4276,10 @@
       <c r="B258" t="n">
         <v>3.11</v>
       </c>
-      <c r="C258" t="n">
-        <v>4.07</v>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="259">
@@ -3779,8 +4291,10 @@
       <c r="B259" t="n">
         <v>3.12</v>
       </c>
-      <c r="C259" t="n">
-        <v>4.07</v>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="260">
@@ -3792,8 +4306,10 @@
       <c r="B260" t="n">
         <v>3.22</v>
       </c>
-      <c r="C260" t="n">
-        <v>4.07</v>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="261">
@@ -3805,8 +4321,10 @@
       <c r="B261" t="n">
         <v>3.14</v>
       </c>
-      <c r="C261" t="n">
-        <v>4.08</v>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="262">
@@ -3818,8 +4336,10 @@
       <c r="B262" t="n">
         <v>3.19</v>
       </c>
-      <c r="C262" t="n">
-        <v>4.08</v>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="263">
@@ -3831,8 +4351,10 @@
       <c r="B263" t="n">
         <v>3.17</v>
       </c>
-      <c r="C263" t="n">
-        <v>4.06</v>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -3844,8 +4366,10 @@
       <c r="B264" t="n">
         <v>3.15</v>
       </c>
-      <c r="C264" t="n">
-        <v>4.06</v>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="265">
@@ -3857,8 +4381,10 @@
       <c r="B265" t="n">
         <v>3.13</v>
       </c>
-      <c r="C265" t="n">
-        <v>4.07</v>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="266">
@@ -3870,8 +4396,10 @@
       <c r="B266" t="n">
         <v>3.13</v>
       </c>
-      <c r="C266" t="n">
-        <v>4.07</v>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -3883,8 +4411,10 @@
       <c r="B267" t="n">
         <v>3.11</v>
       </c>
-      <c r="C267" t="n">
-        <v>4.08</v>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="268">
@@ -3896,8 +4426,10 @@
       <c r="B268" t="n">
         <v>3.12</v>
       </c>
-      <c r="C268" t="n">
-        <v>4.08</v>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="269">
@@ -3909,8 +4441,10 @@
       <c r="B269" t="n">
         <v>3.11</v>
       </c>
-      <c r="C269" t="n">
-        <v>4.08</v>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="270">
@@ -3922,8 +4456,10 @@
       <c r="B270" t="n">
         <v>3.11</v>
       </c>
-      <c r="C270" t="n">
-        <v>4.08</v>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="271">
@@ -3935,8 +4471,10 @@
       <c r="B271" t="n">
         <v>3.14</v>
       </c>
-      <c r="C271" t="n">
-        <v>4.08</v>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="272">
@@ -3948,8 +4486,10 @@
       <c r="B272" t="n">
         <v>3.17</v>
       </c>
-      <c r="C272" t="n">
-        <v>4.07</v>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="273">
@@ -3961,8 +4501,10 @@
       <c r="B273" t="n">
         <v>3.17</v>
       </c>
-      <c r="C273" t="n">
-        <v>4.12</v>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="274">
@@ -3974,8 +4516,10 @@
       <c r="B274" t="n">
         <v>3.18</v>
       </c>
-      <c r="C274" t="n">
-        <v>4.11</v>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="275">
@@ -3987,8 +4531,10 @@
       <c r="B275" t="n">
         <v>3.15</v>
       </c>
-      <c r="C275" t="n">
-        <v>4.11</v>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="276">
@@ -4000,8 +4546,10 @@
       <c r="B276" t="n">
         <v>3.13</v>
       </c>
-      <c r="C276" t="n">
-        <v>4.11</v>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="277">
@@ -4013,8 +4561,10 @@
       <c r="B277" t="n">
         <v>3.18</v>
       </c>
-      <c r="C277" t="n">
-        <v>4.09</v>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="278">
@@ -4026,8 +4576,10 @@
       <c r="B278" t="n">
         <v>3.3</v>
       </c>
-      <c r="C278" t="n">
-        <v>4.09</v>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="279">
@@ -4039,8 +4591,10 @@
       <c r="B279" t="n">
         <v>3.33</v>
       </c>
-      <c r="C279" t="n">
-        <v>4.07</v>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="280">
@@ -4052,8 +4606,10 @@
       <c r="B280" t="n">
         <v>3.36</v>
       </c>
-      <c r="C280" t="n">
-        <v>4.07</v>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="281">
@@ -4065,8 +4621,10 @@
       <c r="B281" t="n">
         <v>3.32</v>
       </c>
-      <c r="C281" t="n">
-        <v>4.05</v>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="282">
@@ -4078,8 +4636,10 @@
       <c r="B282" t="n">
         <v>3.47</v>
       </c>
-      <c r="C282" t="n">
-        <v>4.05</v>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="283">
@@ -4091,8 +4651,10 @@
       <c r="B283" t="n">
         <v>3.31</v>
       </c>
-      <c r="C283" t="n">
-        <v>4.06</v>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="284">
@@ -4104,8 +4666,10 @@
       <c r="B284" t="n">
         <v>3.26</v>
       </c>
-      <c r="C284" t="n">
-        <v>4.05</v>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="285">
@@ -4117,8 +4681,10 @@
       <c r="B285" t="n">
         <v>3.24</v>
       </c>
-      <c r="C285" t="n">
-        <v>4.07</v>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="286">
@@ -4130,8 +4696,10 @@
       <c r="B286" t="n">
         <v>3.24</v>
       </c>
-      <c r="C286" t="n">
-        <v>4.08</v>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="287">
@@ -4143,8 +4711,10 @@
       <c r="B287" t="n">
         <v>3.22</v>
       </c>
-      <c r="C287" t="n">
-        <v>4.07</v>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="288">
@@ -4156,8 +4726,10 @@
       <c r="B288" t="n">
         <v>3.22</v>
       </c>
-      <c r="C288" t="n">
-        <v>4.07</v>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="289">
@@ -4169,8 +4741,10 @@
       <c r="B289" t="n">
         <v>3.25</v>
       </c>
-      <c r="C289" t="n">
-        <v>4.05</v>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="290">
@@ -4182,8 +4756,10 @@
       <c r="B290" t="n">
         <v>3.22</v>
       </c>
-      <c r="C290" t="n">
-        <v>4.06</v>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="291">
@@ -4195,8 +4771,10 @@
       <c r="B291" t="n">
         <v>3.17</v>
       </c>
-      <c r="C291" t="n">
-        <v>4.06</v>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="292">
@@ -4208,8 +4786,10 @@
       <c r="B292" t="n">
         <v>3.13</v>
       </c>
-      <c r="C292" t="n">
-        <v>4.06</v>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="293">
@@ -4221,8 +4801,10 @@
       <c r="B293" t="n">
         <v>3.1</v>
       </c>
-      <c r="C293" t="n">
-        <v>4.06</v>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="294">
@@ -4234,8 +4816,10 @@
       <c r="B294" t="n">
         <v>3.09</v>
       </c>
-      <c r="C294" t="n">
-        <v>4.08</v>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="295">
@@ -4247,8 +4831,10 @@
       <c r="B295" t="n">
         <v>3.08</v>
       </c>
-      <c r="C295" t="n">
-        <v>4.09</v>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="296">
@@ -4260,8 +4846,10 @@
       <c r="B296" t="n">
         <v>3.13</v>
       </c>
-      <c r="C296" t="n">
-        <v>4.1</v>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="297">
@@ -4273,8 +4861,10 @@
       <c r="B297" t="n">
         <v>3.1</v>
       </c>
-      <c r="C297" t="n">
-        <v>4.11</v>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="298">
@@ -4286,8 +4876,10 @@
       <c r="B298" t="n">
         <v>3.09</v>
       </c>
-      <c r="C298" t="n">
-        <v>4.08</v>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="299">
@@ -4299,8 +4891,10 @@
       <c r="B299" t="n">
         <v>3.09</v>
       </c>
-      <c r="C299" t="n">
-        <v>4.09</v>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="300">
@@ -4312,8 +4906,10 @@
       <c r="B300" t="n">
         <v>3.1</v>
       </c>
-      <c r="C300" t="n">
-        <v>4.11</v>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="301">
@@ -4325,8 +4921,10 @@
       <c r="B301" t="n">
         <v>3.09</v>
       </c>
-      <c r="C301" t="n">
-        <v>4.1</v>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="302">
@@ -4338,8 +4936,10 @@
       <c r="B302" t="n">
         <v>3.09</v>
       </c>
-      <c r="C302" t="n">
-        <v>4.07</v>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="303">
@@ -4351,8 +4951,10 @@
       <c r="B303" t="n">
         <v>3.1</v>
       </c>
-      <c r="C303" t="n">
-        <v>4.08</v>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="304">
@@ -4364,8 +4966,10 @@
       <c r="B304" t="n">
         <v>3.05</v>
       </c>
-      <c r="C304" t="n">
-        <v>4.08</v>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="305">
@@ -4377,8 +4981,10 @@
       <c r="B305" t="n">
         <v>3.03</v>
       </c>
-      <c r="C305" t="n">
-        <v>4.06</v>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="306">
@@ -4390,8 +4996,10 @@
       <c r="B306" t="n">
         <v>3.06</v>
       </c>
-      <c r="C306" t="n">
-        <v>4.06</v>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="307">
@@ -4403,8 +5011,10 @@
       <c r="B307" t="n">
         <v>3.07</v>
       </c>
-      <c r="C307" t="n">
-        <v>4.07</v>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="308">
@@ -4416,8 +5026,10 @@
       <c r="B308" t="n">
         <v>3.06</v>
       </c>
-      <c r="C308" t="n">
-        <v>4.07</v>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="309">
@@ -4429,8 +5041,10 @@
       <c r="B309" t="n">
         <v>3.06</v>
       </c>
-      <c r="C309" t="n">
-        <v>4.07</v>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="310">
@@ -4442,8 +5056,10 @@
       <c r="B310" t="n">
         <v>3.06</v>
       </c>
-      <c r="C310" t="n">
-        <v>4.08</v>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="311">
@@ -4455,8 +5071,10 @@
       <c r="B311" t="n">
         <v>3.11</v>
       </c>
-      <c r="C311" t="n">
-        <v>4.08</v>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="312">
@@ -4468,8 +5086,10 @@
       <c r="B312" t="n">
         <v>3.1</v>
       </c>
-      <c r="C312" t="n">
-        <v>4.08</v>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="313">
@@ -4481,8 +5101,10 @@
       <c r="B313" t="n">
         <v>3.11</v>
       </c>
-      <c r="C313" t="n">
-        <v>4.07</v>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="314">
@@ -4494,8 +5116,10 @@
       <c r="B314" t="n">
         <v>3.11</v>
       </c>
-      <c r="C314" t="n">
-        <v>4.07</v>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="315">
@@ -4507,8 +5131,10 @@
       <c r="B315" t="n">
         <v>3.03</v>
       </c>
-      <c r="C315" t="n">
-        <v>4.08</v>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="316">
@@ -4520,8 +5146,10 @@
       <c r="B316" t="n">
         <v>3.04</v>
       </c>
-      <c r="C316" t="n">
-        <v>4.07</v>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="317">
@@ -4533,8 +5161,10 @@
       <c r="B317" t="n">
         <v>3.02</v>
       </c>
-      <c r="C317" t="n">
-        <v>4.1</v>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="318">
@@ -4546,8 +5176,10 @@
       <c r="B318" t="n">
         <v>3.06</v>
       </c>
-      <c r="C318" t="n">
-        <v>4.13</v>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
       </c>
     </row>
     <row r="319">
@@ -4559,8 +5191,10 @@
       <c r="B319" t="n">
         <v>3.05</v>
       </c>
-      <c r="C319" t="n">
-        <v>4.11</v>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="320">
@@ -4572,8 +5206,10 @@
       <c r="B320" t="n">
         <v>3.04</v>
       </c>
-      <c r="C320" t="n">
-        <v>4.12</v>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="321">
@@ -4585,8 +5221,10 @@
       <c r="B321" t="n">
         <v>3.01</v>
       </c>
-      <c r="C321" t="n">
-        <v>4.12</v>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="322">
@@ -4598,8 +5236,10 @@
       <c r="B322" t="n">
         <v>3.02</v>
       </c>
-      <c r="C322" t="n">
-        <v>4.12</v>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="323">
@@ -4611,8 +5251,10 @@
       <c r="B323" t="n">
         <v>3.04</v>
       </c>
-      <c r="C323" t="n">
-        <v>4.1</v>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="324">
@@ -4624,8 +5266,10 @@
       <c r="B324" t="n">
         <v>3.03</v>
       </c>
-      <c r="C324" t="n">
-        <v>4.1</v>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="325">
@@ -4637,8 +5281,10 @@
       <c r="B325" t="n">
         <v>3.02</v>
       </c>
-      <c r="C325" t="n">
-        <v>4.12</v>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="326">
@@ -4650,8 +5296,10 @@
       <c r="B326" t="n">
         <v>3.01</v>
       </c>
-      <c r="C326" t="n">
-        <v>4.12</v>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="327">
@@ -4663,8 +5311,10 @@
       <c r="B327" t="n">
         <v>3.01</v>
       </c>
-      <c r="C327" t="n">
-        <v>4.13</v>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
       </c>
     </row>
     <row r="328">
@@ -4676,8 +5326,10 @@
       <c r="B328" t="n">
         <v>3.02</v>
       </c>
-      <c r="C328" t="n">
-        <v>4.11</v>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="329">
@@ -4689,8 +5341,10 @@
       <c r="B329" t="n">
         <v>3.01</v>
       </c>
-      <c r="C329" t="n">
-        <v>4.11</v>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="330">
@@ -4702,8 +5356,10 @@
       <c r="B330" t="n">
         <v>3.02</v>
       </c>
-      <c r="C330" t="n">
-        <v>4.11</v>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="331">
@@ -4715,8 +5371,10 @@
       <c r="B331" t="n">
         <v>3.02</v>
       </c>
-      <c r="C331" t="n">
-        <v>4.1</v>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="332">
@@ -4728,8 +5386,10 @@
       <c r="B332" t="n">
         <v>3.02</v>
       </c>
-      <c r="C332" t="n">
-        <v>4.1</v>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="333">
@@ -4741,8 +5401,10 @@
       <c r="B333" t="n">
         <v>2.98</v>
       </c>
-      <c r="C333" t="n">
-        <v>4.09</v>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="334">
@@ -4754,8 +5416,10 @@
       <c r="B334" t="n">
         <v>2.95</v>
       </c>
-      <c r="C334" t="n">
-        <v>4.09</v>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="335">
@@ -4767,8 +5431,10 @@
       <c r="B335" t="n">
         <v>2.91</v>
       </c>
-      <c r="C335" t="n">
-        <v>4.1</v>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="336">
@@ -4780,8 +5446,10 @@
       <c r="B336" t="n">
         <v>2.91</v>
       </c>
-      <c r="C336" t="n">
-        <v>4.1</v>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="337">
@@ -4793,8 +5461,10 @@
       <c r="B337" t="n">
         <v>2.9</v>
       </c>
-      <c r="C337" t="n">
-        <v>4.1</v>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -4806,8 +5476,10 @@
       <c r="B338" t="n">
         <v>2.92</v>
       </c>
-      <c r="C338" t="n">
-        <v>4.09</v>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="339">
@@ -4819,8 +5491,10 @@
       <c r="B339" t="n">
         <v>2.91</v>
       </c>
-      <c r="C339" t="n">
-        <v>4.11</v>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="340">
@@ -4832,8 +5506,10 @@
       <c r="B340" t="n">
         <v>2.92</v>
       </c>
-      <c r="C340" t="n">
-        <v>4.1</v>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="341">
@@ -4845,8 +5521,10 @@
       <c r="B341" t="n">
         <v>2.92</v>
       </c>
-      <c r="C341" t="n">
-        <v>4.09</v>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="342">
@@ -4858,8 +5536,10 @@
       <c r="B342" t="n">
         <v>2.93</v>
       </c>
-      <c r="C342" t="n">
-        <v>4.12</v>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="343">
@@ -4871,8 +5551,10 @@
       <c r="B343" t="n">
         <v>2.93</v>
       </c>
-      <c r="C343" t="n">
-        <v>4.12</v>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="344">
@@ -4884,8 +5566,10 @@
       <c r="B344" t="n">
         <v>2.93</v>
       </c>
-      <c r="C344" t="n">
-        <v>4.08</v>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="345">
@@ -4897,8 +5581,10 @@
       <c r="B345" t="n">
         <v>2.97</v>
       </c>
-      <c r="C345" t="n">
-        <v>4.08</v>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="346">
@@ -4910,8 +5596,10 @@
       <c r="B346" t="n">
         <v>2.96</v>
       </c>
-      <c r="C346" t="n">
-        <v>4.08</v>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="347">
@@ -4923,8 +5611,10 @@
       <c r="B347" t="n">
         <v>2.95</v>
       </c>
-      <c r="C347" t="n">
-        <v>4.08</v>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="348">
@@ -4936,8 +5626,10 @@
       <c r="B348" t="n">
         <v>3</v>
       </c>
-      <c r="C348" t="n">
-        <v>4.09</v>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="349">
@@ -4949,8 +5641,10 @@
       <c r="B349" t="n">
         <v>3</v>
       </c>
-      <c r="C349" t="n">
-        <v>4.07</v>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="350">
@@ -4962,8 +5656,10 @@
       <c r="B350" t="n">
         <v>3.03</v>
       </c>
-      <c r="C350" t="n">
-        <v>4.07</v>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="351">
@@ -4975,8 +5671,10 @@
       <c r="B351" t="n">
         <v>3.08</v>
       </c>
-      <c r="C351" t="n">
-        <v>4.08</v>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="352">
@@ -4988,8 +5686,10 @@
       <c r="B352" t="n">
         <v>3.05</v>
       </c>
-      <c r="C352" t="n">
-        <v>4.07</v>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="353">
@@ -5001,8 +5701,10 @@
       <c r="B353" t="n">
         <v>3.03</v>
       </c>
-      <c r="C353" t="n">
-        <v>4.08</v>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="354">
@@ -5014,8 +5716,10 @@
       <c r="B354" t="n">
         <v>3.05</v>
       </c>
-      <c r="C354" t="n">
-        <v>4.08</v>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="355">
@@ -5027,8 +5731,10 @@
       <c r="B355" t="n">
         <v>2.99</v>
       </c>
-      <c r="C355" t="n">
-        <v>4.07</v>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="356">
@@ -5040,8 +5746,10 @@
       <c r="B356" t="n">
         <v>2.97</v>
       </c>
-      <c r="C356" t="n">
-        <v>4.06</v>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="357">
@@ -5053,8 +5761,10 @@
       <c r="B357" t="n">
         <v>2.99</v>
       </c>
-      <c r="C357" t="n">
-        <v>4.05</v>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="358">
@@ -5066,8 +5776,10 @@
       <c r="B358" t="n">
         <v>2.99</v>
       </c>
-      <c r="C358" t="n">
-        <v>4.04</v>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="359">
@@ -5079,8 +5791,10 @@
       <c r="B359" t="n">
         <v>2.98</v>
       </c>
-      <c r="C359" t="n">
-        <v>4.05</v>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="360">
@@ -5092,8 +5806,10 @@
       <c r="B360" t="n">
         <v>2.95</v>
       </c>
-      <c r="C360" t="n">
-        <v>4.05</v>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="361">
@@ -5105,8 +5821,10 @@
       <c r="B361" t="n">
         <v>3.01</v>
       </c>
-      <c r="C361" t="n">
-        <v>4.06</v>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="362">
@@ -5118,8 +5836,10 @@
       <c r="B362" t="n">
         <v>2.99</v>
       </c>
-      <c r="C362" t="n">
-        <v>4.1</v>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="363">
@@ -5131,8 +5851,10 @@
       <c r="B363" t="n">
         <v>3</v>
       </c>
-      <c r="C363" t="n">
-        <v>4.08</v>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="364">
@@ -5144,8 +5866,10 @@
       <c r="B364" t="n">
         <v>2.97</v>
       </c>
-      <c r="C364" t="n">
-        <v>4.1</v>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="365">
@@ -5157,8 +5881,10 @@
       <c r="B365" t="n">
         <v>2.96</v>
       </c>
-      <c r="C365" t="n">
-        <v>4.09</v>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="366">
@@ -5170,8 +5896,10 @@
       <c r="B366" t="n">
         <v>2.99</v>
       </c>
-      <c r="C366" t="n">
-        <v>4.08</v>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="367">
@@ -5183,8 +5911,10 @@
       <c r="B367" t="n">
         <v>2.97</v>
       </c>
-      <c r="C367" t="n">
-        <v>4.09</v>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="368">
@@ -5196,8 +5926,10 @@
       <c r="B368" t="n">
         <v>3.01</v>
       </c>
-      <c r="C368" t="n">
-        <v>4.08</v>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="369">
@@ -5209,8 +5941,10 @@
       <c r="B369" t="n">
         <v>3.05</v>
       </c>
-      <c r="C369" t="n">
-        <v>4.09</v>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="370">
@@ -5222,8 +5956,10 @@
       <c r="B370" t="n">
         <v>3</v>
       </c>
-      <c r="C370" t="n">
-        <v>4.09</v>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="371">
@@ -5235,8 +5971,10 @@
       <c r="B371" t="n">
         <v>2.94</v>
       </c>
-      <c r="C371" t="n">
-        <v>4.1</v>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="372">
@@ -5248,8 +5986,10 @@
       <c r="B372" t="n">
         <v>2.99</v>
       </c>
-      <c r="C372" t="n">
-        <v>4.1</v>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="373">
@@ -5261,8 +6001,10 @@
       <c r="B373" t="n">
         <v>3.01</v>
       </c>
-      <c r="C373" t="n">
-        <v>4.1</v>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="374">
@@ -5274,8 +6016,10 @@
       <c r="B374" t="n">
         <v>2.99</v>
       </c>
-      <c r="C374" t="n">
-        <v>4.09</v>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="375">
@@ -5287,8 +6031,10 @@
       <c r="B375" t="n">
         <v>3.03</v>
       </c>
-      <c r="C375" t="n">
-        <v>4.1</v>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="376">
@@ -5300,8 +6046,10 @@
       <c r="B376" t="n">
         <v>3</v>
       </c>
-      <c r="C376" t="n">
-        <v>4.09</v>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="377">
@@ -5313,8 +6061,10 @@
       <c r="B377" t="n">
         <v>3.02</v>
       </c>
-      <c r="C377" t="n">
-        <v>4.09</v>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="378">
@@ -5326,8 +6076,10 @@
       <c r="B378" t="n">
         <v>2.95</v>
       </c>
-      <c r="C378" t="n">
-        <v>4.09</v>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="379">
@@ -5339,8 +6091,10 @@
       <c r="B379" t="n">
         <v>2.94</v>
       </c>
-      <c r="C379" t="n">
-        <v>4.08</v>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="380">
@@ -5352,8 +6106,10 @@
       <c r="B380" t="n">
         <v>2.92</v>
       </c>
-      <c r="C380" t="n">
-        <v>4.08</v>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="381">
@@ -5365,8 +6121,10 @@
       <c r="B381" t="n">
         <v>2.91</v>
       </c>
-      <c r="C381" t="n">
-        <v>4.08</v>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="382">
@@ -5378,8 +6136,10 @@
       <c r="B382" t="n">
         <v>2.89</v>
       </c>
-      <c r="C382" t="n">
-        <v>4.07</v>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="383">
@@ -5391,8 +6151,10 @@
       <c r="B383" t="n">
         <v>2.94</v>
       </c>
-      <c r="C383" t="n">
-        <v>4.1</v>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="384">
@@ -5404,8 +6166,10 @@
       <c r="B384" t="n">
         <v>2.94</v>
       </c>
-      <c r="C384" t="n">
-        <v>4.1</v>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="385">
@@ -5417,8 +6181,10 @@
       <c r="B385" t="n">
         <v>2.98</v>
       </c>
-      <c r="C385" t="n">
-        <v>4.1</v>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="386">
@@ -5430,8 +6196,10 @@
       <c r="B386" t="n">
         <v>2.95</v>
       </c>
-      <c r="C386" t="n">
-        <v>4.11</v>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="387">
@@ -5443,8 +6211,10 @@
       <c r="B387" t="n">
         <v>2.92</v>
       </c>
-      <c r="C387" t="n">
-        <v>4.1</v>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="388">
@@ -5456,8 +6226,10 @@
       <c r="B388" t="n">
         <v>2.9</v>
       </c>
-      <c r="C388" t="n">
-        <v>4.1</v>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="389">
@@ -5469,8 +6241,10 @@
       <c r="B389" t="n">
         <v>2.88</v>
       </c>
-      <c r="C389" t="n">
-        <v>4.12</v>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="390">
@@ -5482,8 +6256,10 @@
       <c r="B390" t="n">
         <v>2.91</v>
       </c>
-      <c r="C390" t="n">
-        <v>4.08</v>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="391">
@@ -5495,8 +6271,10 @@
       <c r="B391" t="n">
         <v>2.9</v>
       </c>
-      <c r="C391" t="n">
-        <v>4.09</v>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="392">
@@ -5508,8 +6286,10 @@
       <c r="B392" t="n">
         <v>2.87</v>
       </c>
-      <c r="C392" t="n">
-        <v>4.08</v>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="393">
@@ -5521,8 +6301,10 @@
       <c r="B393" t="n">
         <v>2.89</v>
       </c>
-      <c r="C393" t="n">
-        <v>4.08</v>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="394">
@@ -5534,8 +6316,10 @@
       <c r="B394" t="n">
         <v>2.87</v>
       </c>
-      <c r="C394" t="n">
-        <v>4.07</v>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="395">
@@ -5547,8 +6331,10 @@
       <c r="B395" t="n">
         <v>2.88</v>
       </c>
-      <c r="C395" t="n">
-        <v>4.07</v>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="396">
@@ -5560,8 +6346,10 @@
       <c r="B396" t="n">
         <v>2.9</v>
       </c>
-      <c r="C396" t="n">
-        <v>4.07</v>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="397">
@@ -5573,8 +6361,10 @@
       <c r="B397" t="n">
         <v>2.9</v>
       </c>
-      <c r="C397" t="n">
-        <v>4.08</v>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="398">
@@ -5586,8 +6376,10 @@
       <c r="B398" t="n">
         <v>2.9</v>
       </c>
-      <c r="C398" t="n">
-        <v>4.07</v>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="399">
@@ -5599,8 +6391,10 @@
       <c r="B399" t="n">
         <v>2.89</v>
       </c>
-      <c r="C399" t="n">
-        <v>4.07</v>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="400">
@@ -5612,8 +6406,10 @@
       <c r="B400" t="n">
         <v>2.9</v>
       </c>
-      <c r="C400" t="n">
-        <v>4.07</v>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="401">
@@ -5625,8 +6421,10 @@
       <c r="B401" t="n">
         <v>2.9</v>
       </c>
-      <c r="C401" t="n">
-        <v>4.07</v>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="402">
@@ -5638,8 +6436,10 @@
       <c r="B402" t="n">
         <v>2.99</v>
       </c>
-      <c r="C402" t="n">
-        <v>4.06</v>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="403">
@@ -5651,8 +6451,10 @@
       <c r="B403" t="n">
         <v>2.98</v>
       </c>
-      <c r="C403" t="n">
-        <v>4.05</v>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="404">
@@ -5664,8 +6466,10 @@
       <c r="B404" t="n">
         <v>2.97</v>
       </c>
-      <c r="C404" t="n">
-        <v>4.05</v>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="405">
@@ -5677,8 +6481,10 @@
       <c r="B405" t="n">
         <v>2.99</v>
       </c>
-      <c r="C405" t="n">
-        <v>4.07</v>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="406">
@@ -5690,8 +6496,10 @@
       <c r="B406" t="n">
         <v>2.97</v>
       </c>
-      <c r="C406" t="n">
-        <v>4.08</v>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="407">
@@ -5703,8 +6511,10 @@
       <c r="B407" t="n">
         <v>2.96</v>
       </c>
-      <c r="C407" t="n">
-        <v>4.06</v>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="408">
@@ -5716,8 +6526,10 @@
       <c r="B408" t="n">
         <v>2.96</v>
       </c>
-      <c r="C408" t="n">
-        <v>4.06</v>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="409">
@@ -5729,8 +6541,10 @@
       <c r="B409" t="n">
         <v>2.95</v>
       </c>
-      <c r="C409" t="n">
-        <v>4.06</v>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="410">
@@ -5742,8 +6556,10 @@
       <c r="B410" t="n">
         <v>2.96</v>
       </c>
-      <c r="C410" t="n">
-        <v>4.07</v>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="411">
@@ -5755,8 +6571,10 @@
       <c r="B411" t="n">
         <v>2.96</v>
       </c>
-      <c r="C411" t="n">
-        <v>4.07</v>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="412">
@@ -5768,8 +6586,10 @@
       <c r="B412" t="n">
         <v>3</v>
       </c>
-      <c r="C412" t="n">
-        <v>4.07</v>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="413">
@@ -5781,8 +6601,10 @@
       <c r="B413" t="n">
         <v>3.05</v>
       </c>
-      <c r="C413" t="n">
-        <v>4.08</v>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="414">
@@ -5794,8 +6616,10 @@
       <c r="B414" t="n">
         <v>3.05</v>
       </c>
-      <c r="C414" t="n">
-        <v>4.08</v>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="415">
@@ -5807,8 +6631,10 @@
       <c r="B415" t="n">
         <v>3.05</v>
       </c>
-      <c r="C415" t="n">
-        <v>4.08</v>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="416">
@@ -5820,8 +6646,10 @@
       <c r="B416" t="n">
         <v>2.96</v>
       </c>
-      <c r="C416" t="n">
-        <v>4.08</v>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="417">
@@ -5833,8 +6661,10 @@
       <c r="B417" t="n">
         <v>2.96</v>
       </c>
-      <c r="C417" t="n">
-        <v>4.08</v>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="418">
@@ -5846,8 +6676,10 @@
       <c r="B418" t="n">
         <v>2.99</v>
       </c>
-      <c r="C418" t="n">
-        <v>4.09</v>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="419">
@@ -5859,8 +6691,10 @@
       <c r="B419" t="n">
         <v>2.96</v>
       </c>
-      <c r="C419" t="n">
-        <v>4.09</v>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="420">
@@ -5872,8 +6706,10 @@
       <c r="B420" t="n">
         <v>2.94</v>
       </c>
-      <c r="C420" t="n">
-        <v>4.1</v>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="421">
@@ -5885,8 +6721,10 @@
       <c r="B421" t="n">
         <v>2.95</v>
       </c>
-      <c r="C421" t="n">
-        <v>4.1</v>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="422">
@@ -5898,8 +6736,10 @@
       <c r="B422" t="n">
         <v>2.95</v>
       </c>
-      <c r="C422" t="n">
-        <v>4.09</v>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="423">
@@ -5911,8 +6751,10 @@
       <c r="B423" t="n">
         <v>2.92</v>
       </c>
-      <c r="C423" t="n">
-        <v>4.08</v>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="424">
@@ -5924,8 +6766,10 @@
       <c r="B424" t="n">
         <v>2.88</v>
       </c>
-      <c r="C424" t="n">
-        <v>4.09</v>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="425">
@@ -5937,8 +6781,10 @@
       <c r="B425" t="n">
         <v>2.89</v>
       </c>
-      <c r="C425" t="n">
-        <v>4.11</v>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="426">
@@ -5950,8 +6796,10 @@
       <c r="B426" t="n">
         <v>2.91</v>
       </c>
-      <c r="C426" t="n">
-        <v>4.09</v>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="427">
@@ -5963,8 +6811,10 @@
       <c r="B427" t="n">
         <v>2.97</v>
       </c>
-      <c r="C427" t="n">
-        <v>4.09</v>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="428">
@@ -5976,8 +6826,10 @@
       <c r="B428" t="n">
         <v>2.99</v>
       </c>
-      <c r="C428" t="n">
-        <v>4.13</v>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
       </c>
     </row>
     <row r="429">
@@ -5989,8 +6841,10 @@
       <c r="B429" t="n">
         <v>2.98</v>
       </c>
-      <c r="C429" t="n">
-        <v>4.12</v>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="430">
@@ -6002,8 +6856,10 @@
       <c r="B430" t="n">
         <v>3.06</v>
       </c>
-      <c r="C430" t="n">
-        <v>4.13</v>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
       </c>
     </row>
     <row r="431">
@@ -6015,8 +6871,10 @@
       <c r="B431" t="n">
         <v>3.05</v>
       </c>
-      <c r="C431" t="n">
-        <v>4.12</v>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="432">
@@ -6028,8 +6886,10 @@
       <c r="B432" t="n">
         <v>3.01</v>
       </c>
-      <c r="C432" t="n">
-        <v>4.14</v>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
       </c>
     </row>
     <row r="433">
@@ -6041,8 +6901,10 @@
       <c r="B433" t="n">
         <v>3.02</v>
       </c>
-      <c r="C433" t="n">
-        <v>4.14</v>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
       </c>
     </row>
     <row r="434">
@@ -6054,8 +6916,10 @@
       <c r="B434" t="n">
         <v>2.96</v>
       </c>
-      <c r="C434" t="n">
-        <v>4.12</v>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="435">
@@ -6067,8 +6931,10 @@
       <c r="B435" t="n">
         <v>2.96</v>
       </c>
-      <c r="C435" t="n">
-        <v>4.12</v>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="436">
@@ -6080,8 +6946,10 @@
       <c r="B436" t="n">
         <v>2.93</v>
       </c>
-      <c r="C436" t="n">
-        <v>4.12</v>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="437">
@@ -6093,8 +6961,10 @@
       <c r="B437" t="n">
         <v>2.99</v>
       </c>
-      <c r="C437" t="n">
-        <v>4.12</v>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="438">
@@ -6106,8 +6976,10 @@
       <c r="B438" t="n">
         <v>3</v>
       </c>
-      <c r="C438" t="n">
-        <v>4.12</v>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="439">
@@ -6119,8 +6991,10 @@
       <c r="B439" t="n">
         <v>3.04</v>
       </c>
-      <c r="C439" t="n">
-        <v>4.13</v>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
       </c>
     </row>
     <row r="440">
@@ -6132,8 +7006,10 @@
       <c r="B440" t="n">
         <v>3.02</v>
       </c>
-      <c r="C440" t="n">
-        <v>4.11</v>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="441">
@@ -6145,8 +7021,10 @@
       <c r="B441" t="n">
         <v>3</v>
       </c>
-      <c r="C441" t="n">
-        <v>4.12</v>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
     </row>
     <row r="442">
@@ -6158,8 +7036,10 @@
       <c r="B442" t="n">
         <v>3</v>
       </c>
-      <c r="C442" t="n">
-        <v>4.11</v>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
       </c>
     </row>
     <row r="443">
@@ -6171,8 +7051,10 @@
       <c r="B443" t="n">
         <v>2.99</v>
       </c>
-      <c r="C443" t="n">
-        <v>4.1</v>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="444">
@@ -6184,8 +7066,10 @@
       <c r="B444" t="n">
         <v>2.99</v>
       </c>
-      <c r="C444" t="n">
-        <v>4.1</v>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
     </row>
     <row r="445">
@@ -6197,8 +7081,10 @@
       <c r="B445" t="n">
         <v>2.91</v>
       </c>
-      <c r="C445" t="n">
-        <v>4.08</v>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="446">
@@ -6210,8 +7096,10 @@
       <c r="B446" t="n">
         <v>2.85</v>
       </c>
-      <c r="C446" t="n">
-        <v>4.08</v>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="447">
@@ -6223,8 +7111,10 @@
       <c r="B447" t="n">
         <v>2.85</v>
       </c>
-      <c r="C447" t="n">
-        <v>4.08</v>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="448">
@@ -6236,8 +7126,10 @@
       <c r="B448" t="n">
         <v>2.85</v>
       </c>
-      <c r="C448" t="n">
-        <v>4.08</v>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="449">
@@ -6249,8 +7141,10 @@
       <c r="B449" t="n">
         <v>2.91</v>
       </c>
-      <c r="C449" t="n">
-        <v>4.08</v>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="450">
@@ -6262,8 +7156,10 @@
       <c r="B450" t="n">
         <v>2.9</v>
       </c>
-      <c r="C450" t="n">
-        <v>4.09</v>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
       </c>
     </row>
     <row r="451">
@@ -6275,8 +7171,10 @@
       <c r="B451" t="n">
         <v>2.88</v>
       </c>
-      <c r="C451" t="n">
-        <v>4.08</v>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
       </c>
     </row>
     <row r="452">
@@ -6288,8 +7186,10 @@
       <c r="B452" t="n">
         <v>2.9</v>
       </c>
-      <c r="C452" t="n">
-        <v>4.07</v>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="453">
@@ -6301,8 +7201,10 @@
       <c r="B453" t="n">
         <v>2.9</v>
       </c>
-      <c r="C453" t="n">
-        <v>4.07</v>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
       </c>
     </row>
     <row r="454">
@@ -6314,8 +7216,10 @@
       <c r="B454" t="n">
         <v>2.92</v>
       </c>
-      <c r="C454" t="n">
-        <v>4.06</v>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
       </c>
     </row>
     <row r="455">
@@ -6327,8 +7231,10 @@
       <c r="B455" t="n">
         <v>2.95</v>
       </c>
-      <c r="C455" t="n">
-        <v>4.05</v>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="456">
@@ -6340,8 +7246,10 @@
       <c r="B456" t="n">
         <v>2.96</v>
       </c>
-      <c r="C456" t="n">
-        <v>4.04</v>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="457">
@@ -6353,8 +7261,10 @@
       <c r="B457" t="n">
         <v>2.92</v>
       </c>
-      <c r="C457" t="n">
-        <v>4.05</v>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="458">
@@ -6366,8 +7276,10 @@
       <c r="B458" t="n">
         <v>2.94</v>
       </c>
-      <c r="C458" t="n">
-        <v>4.04</v>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
       </c>
     </row>
     <row r="459">
@@ -6379,8 +7291,10 @@
       <c r="B459" t="n">
         <v>2.94</v>
       </c>
-      <c r="C459" t="n">
-        <v>4.02</v>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="460">
@@ -6392,8 +7306,10 @@
       <c r="B460" t="n">
         <v>2.94</v>
       </c>
-      <c r="C460" t="n">
-        <v>4.02</v>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
       </c>
     </row>
     <row r="461">
@@ -6405,8 +7321,10 @@
       <c r="B461" t="n">
         <v>2.98</v>
       </c>
-      <c r="C461" t="n">
-        <v>4.05</v>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="462">
@@ -6418,8 +7336,10 @@
       <c r="B462" t="n">
         <v>2.95</v>
       </c>
-      <c r="C462" t="n">
-        <v>4.05</v>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
       </c>
     </row>
     <row r="463">
@@ -6431,8 +7351,10 @@
       <c r="B463" t="n">
         <v>2.94</v>
       </c>
-      <c r="C463" t="n">
-        <v>4.03</v>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="464">
@@ -6444,8 +7366,10 @@
       <c r="B464" t="n">
         <v>2.93</v>
       </c>
-      <c r="C464" t="n">
-        <v>4.01</v>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="465">
@@ -6457,8 +7381,10 @@
       <c r="B465" t="n">
         <v>2.92</v>
       </c>
-      <c r="C465" t="n">
-        <v>4.01</v>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="466">
@@ -6470,8 +7396,10 @@
       <c r="B466" t="n">
         <v>2.9</v>
       </c>
-      <c r="C466" t="n">
-        <v>4</v>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="467">
@@ -6483,8 +7411,10 @@
       <c r="B467" t="n">
         <v>2.9</v>
       </c>
-      <c r="C467" t="n">
-        <v>4</v>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="468">
@@ -6496,8 +7426,10 @@
       <c r="B468" t="n">
         <v>2.91</v>
       </c>
-      <c r="C468" t="n">
-        <v>4</v>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="469">
@@ -6509,8 +7441,10 @@
       <c r="B469" t="n">
         <v>2.89</v>
       </c>
-      <c r="C469" t="n">
-        <v>3.99</v>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
       </c>
     </row>
     <row r="470">
@@ -6522,8 +7456,10 @@
       <c r="B470" t="n">
         <v>2.89</v>
       </c>
-      <c r="C470" t="n">
-        <v>3.99</v>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
       </c>
     </row>
     <row r="471">
@@ -6535,8 +7471,10 @@
       <c r="B471" t="n">
         <v>2.88</v>
       </c>
-      <c r="C471" t="n">
-        <v>3.99</v>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
       </c>
     </row>
     <row r="472">
@@ -6548,8 +7486,10 @@
       <c r="B472" t="n">
         <v>2.88</v>
       </c>
-      <c r="C472" t="n">
-        <v>3.99</v>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
       </c>
     </row>
     <row r="473">
@@ -6561,8 +7501,10 @@
       <c r="B473" t="n">
         <v>2.9</v>
       </c>
-      <c r="C473" t="n">
-        <v>3.99</v>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
       </c>
     </row>
     <row r="474">
@@ -6574,8 +7516,10 @@
       <c r="B474" t="n">
         <v>2.86</v>
       </c>
-      <c r="C474" t="n">
-        <v>3.98</v>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
       </c>
     </row>
     <row r="475">
@@ -6587,8 +7531,10 @@
       <c r="B475" t="n">
         <v>2.86</v>
       </c>
-      <c r="C475" t="n">
-        <v>4</v>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="476">
@@ -6600,8 +7546,10 @@
       <c r="B476" t="n">
         <v>2.87</v>
       </c>
-      <c r="C476" t="n">
-        <v>4.03</v>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="477">
@@ -6613,8 +7561,10 @@
       <c r="B477" t="n">
         <v>2.89</v>
       </c>
-      <c r="C477" t="n">
-        <v>4.03</v>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="478">
@@ -6626,8 +7576,10 @@
       <c r="B478" t="n">
         <v>2.87</v>
       </c>
-      <c r="C478" t="n">
-        <v>4.03</v>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
       </c>
     </row>
     <row r="479">
@@ -6639,8 +7591,10 @@
       <c r="B479" t="n">
         <v>2.88</v>
       </c>
-      <c r="C479" t="n">
-        <v>4.01</v>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="480">
@@ -6652,21 +7606,1358 @@
       <c r="B480" t="n">
         <v>2.87</v>
       </c>
-      <c r="C480" t="n">
-        <v>4.01</v>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>4.02_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>4.04_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>4.03_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>4.03_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>4.02_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>4.02_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>4.05_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>4.03_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>4.03_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>4.03_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>4.02_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>4.05_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>4.1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>4.1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>4.07_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>4.1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>4.11_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>4.07_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>4.06_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>4.07_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>4.07_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>4.04_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="B481" t="n">
+      <c r="B523" t="n">
         <v>3.12</v>
       </c>
-      <c r="C481" t="n">
-        <v>4.11</v>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>4.11_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>4.1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>4.14_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>4.1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>4.06_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>4.05_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>4.05_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>4.05_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>4.04_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>4.05_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>4.06_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>4.12_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>4.11_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>4.1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>4.1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>4.1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>4.1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>4.11_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>4.11_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>4.12_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>4.11_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>4.1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>4.07_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>4.08_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>4.1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>4.11_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>4.11_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>4.11_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>4.11_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>4.12_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>4.09_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="C570" t="n">
+        <v>4.13</v>
       </c>
     </row>
   </sheetData>
